--- a/data/trans_dic/IP21B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,0</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,75</t>
+          <t>0,0; 21,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,69</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,01</t>
+          <t>0,0; 17,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,94</t>
+          <t>0,0; 82,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 53,07</t>
+          <t>6,65; 53,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,84; 74,14</t>
+          <t>17,75; 75,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,61</t>
+          <t>0,0; 72,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 62,27</t>
+          <t>7,6; 57,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 63,94</t>
+          <t>15,83; 60,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,17</t>
+          <t>0,0; 82,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,24</t>
+          <t>0,0; 70,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 54,58</t>
+          <t>14,03; 53,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 48,79</t>
+          <t>17,77; 49,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,37; 69,34</t>
+          <t>20,3; 69,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 57,93</t>
+          <t>8,83; 62,33</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,98</t>
+          <t>0,0; 85,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,61</t>
+          <t>0,0; 56,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 74,69</t>
+          <t>0,0; 80,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 57,59</t>
+          <t>7,79; 58,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 66,72</t>
+          <t>15,45; 65,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,51</t>
+          <t>0,0; 83,26</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,52</t>
+          <t>0,0; 61,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,18</t>
+          <t>0,0; 53,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,81</t>
+          <t>0,0; 50,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,35</t>
+          <t>0,0; 43,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,12</t>
+          <t>0,0; 75,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 21,69</t>
+          <t>2,68; 22,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 30,07</t>
+          <t>5,95; 30,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 39,94</t>
+          <t>9,79; 39,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 51,97</t>
+          <t>6,65; 52,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 22,93</t>
+          <t>4,41; 24,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 31,21</t>
+          <t>9,24; 30,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 40,87</t>
+          <t>9,39; 41,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 54,06</t>
+          <t>6,14; 52,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 19,07</t>
+          <t>5,67; 19,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,26</t>
+          <t>9,56; 25,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 33,65</t>
+          <t>12,76; 33,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 43,04</t>
+          <t>12,21; 45,42</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4249</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3502</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4129</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4340</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2974</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7623</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2274</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3227</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>728; 5906</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1248; 5296</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3273</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>710; 5376</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2001; 7635</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2712</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2278</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1859; 7138</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4194; 11776</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2091; 7130</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>684; 4827</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3684</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1959</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3486</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2058</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2682</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4234</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2776</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>519; 3922</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1443; 6083</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3281</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3775</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4194</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3782</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>681; 5737</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1669; 8673</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2078; 8339</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>613; 4824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1462; 8152</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3001; 9808</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8486</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>765; 6519</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3318; 11486</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5781; 15126</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5348; 14049</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2647; 9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Edad-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 31,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,39</t>
+          <t>0,0; 21,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 10,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,36</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,58</t>
+          <t>0,0; 83,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 53,88</t>
+          <t>6,58; 55,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 75,32</t>
+          <t>17,9; 76,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,17</t>
+          <t>0,0; 81,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 57,55</t>
+          <t>7,79; 57,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 60,41</t>
+          <t>15,39; 60,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,96</t>
+          <t>0,0; 82,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,98</t>
+          <t>0,0; 70,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 53,87</t>
+          <t>10,66; 52,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 49,9</t>
+          <t>17,96; 48,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 69,22</t>
+          <t>24,0; 70,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 62,33</t>
+          <t>8,7; 64,4</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,98</t>
+          <t>0,0; 57,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,24</t>
+          <t>10,36; 74,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 58,84</t>
+          <t>7,5; 64,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 65,1</t>
+          <t>15,02; 69,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,26</t>
+          <t>0,0; 73,16</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,47</t>
+          <t>0,0; 61,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,57</t>
+          <t>0,0; 59,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,63</t>
+          <t>0,0; 48,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,24</t>
+          <t>0,0; 35,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,14</t>
+          <t>0,0; 75,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,58</t>
+          <t>2,29; 20,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 30,95</t>
+          <t>5,56; 29,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 39,28</t>
+          <t>10,16; 40,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 52,35</t>
+          <t>6,65; 51,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,59</t>
+          <t>5,66; 22,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,2</t>
+          <t>8,27; 30,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,0</t>
+          <t>7,71; 39,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,31</t>
+          <t>7,29; 55,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 19,61</t>
+          <t>5,66; 18,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,0</t>
+          <t>9,62; 25,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 33,51</t>
+          <t>12,56; 33,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 45,42</t>
+          <t>11,03; 45,71</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3502</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4129</t>
+          <t>0; 3573</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4340</t>
+          <t>0; 4844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3227</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>728; 5906</t>
+          <t>722; 6068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1248; 5296</t>
+          <t>1259; 5355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>0; 3704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>710; 5376</t>
+          <t>728; 5378</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2001; 7635</t>
+          <t>1945; 7585</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2712</t>
+          <t>0; 2681</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2278</t>
+          <t>0; 2258</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1859; 7138</t>
+          <t>1413; 6931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4194; 11776</t>
+          <t>4239; 11431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2091; 7130</t>
+          <t>2472; 7229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>684; 4827</t>
+          <t>674; 4987</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2682</t>
+          <t>0; 2699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>547; 3909</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>519; 3922</t>
+          <t>500; 4317</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1443; 6083</t>
+          <t>1404; 6466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4025</t>
+          <t>0; 3537</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>0; 3294</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3378</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4194</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>0; 3823</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>681; 5737</t>
+          <t>583; 5282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1669; 8673</t>
+          <t>1559; 8175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2078; 8339</t>
+          <t>2157; 8692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>613; 4824</t>
+          <t>613; 4782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1462; 8152</t>
+          <t>1877; 7536</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3001; 9808</t>
+          <t>2687; 9777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1944; 8486</t>
+          <t>1597; 8186</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>765; 6519</t>
+          <t>908; 6874</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3318; 11486</t>
+          <t>3316; 11013</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5781; 15126</t>
+          <t>5821; 15389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5348; 14049</t>
+          <t>5266; 14230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2647; 9845</t>
+          <t>2390; 9907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,32 +649,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,59%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,5</t>
+          <t>0,0; 10,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 18,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>32,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>27,13%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>46,64%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,56</t>
+          <t>7,55; 62,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 55,36</t>
+          <t>15,9; 63,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 76,15</t>
+          <t>0,0; 82,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,67</t>
+          <t>0,0; 73,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 57,57</t>
+          <t>0,0; 82,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 60,02</t>
+          <t>6,6; 53,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,0</t>
+          <t>17,84; 74,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,36</t>
+          <t>0,0; 83,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 52,31</t>
+          <t>10,63; 54,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 48,44</t>
+          <t>17,59; 48,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 70,18</t>
+          <t>20,37; 69,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 64,4</t>
+          <t>8,07; 63,04</t>
         </is>
       </c>
     </row>
@@ -929,54 +929,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41,43%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>60,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>36,81%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>39,42%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -997,29 +997,29 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 55,61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11,52; 74,69</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 85,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 57,35</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 74,1</t>
+          <t>0,0; 85,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 64,77</t>
+          <t>7,48; 57,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 69,2</t>
+          <t>14,73; 66,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,16</t>
+          <t>0,0; 73,59</t>
         </is>
       </c>
     </row>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,95</t>
+          <t>0,0; 48,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,91</t>
+          <t>0,0; 44,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,95</t>
+          <t>0,0; 79,49</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 20,79</t>
+          <t>4,29; 22,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 29,17</t>
+          <t>8,1; 31,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 40,95</t>
+          <t>7,93; 40,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 51,89</t>
+          <t>7,75; 55,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,73</t>
+          <t>2,51; 21,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 30,1</t>
+          <t>5,22; 30,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 39,55</t>
+          <t>9,84; 39,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 55,16</t>
+          <t>7,54; 55,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,81</t>
+          <t>5,38; 19,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,44</t>
+          <t>9,75; 25,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,94</t>
+          <t>12,2; 33,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 45,71</t>
+          <t>11,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1577,32 +1577,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>719</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>1379</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4588</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3585</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3573</t>
+          <t>0; 3637</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4844</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1289</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2974</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3280</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2231</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>705; 5817</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>722; 6068</t>
+          <t>2009; 8081</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1259; 5355</t>
+          <t>0; 2686</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3704</t>
+          <t>0; 1860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>728; 5378</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1945; 7585</t>
+          <t>724; 5816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2681</t>
+          <t>1254; 5213</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2258</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1413; 6931</t>
+          <t>1409; 7232</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4239; 11431</t>
+          <t>4151; 11514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2472; 7229</t>
+          <t>2098; 7143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>674; 4987</t>
+          <t>561; 4381</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1181</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1497</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>627</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1369</t>
         </is>
       </c>
     </row>
@@ -2061,29 +2061,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 2618</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>608; 3941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2441</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0; 1959</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3486</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2058</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2699</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>547; 3909</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2776</t>
+          <t>0; 1996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>500; 4317</t>
+          <t>498; 3839</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1404; 6466</t>
+          <t>1376; 6234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3265</t>
         </is>
       </c>
     </row>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2206,17 +2206,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2226,37 +2226,37 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>1205</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1756</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3858</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3775</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 4302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 4043</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>583; 5282</t>
+          <t>1421; 7603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1559; 8175</t>
+          <t>2630; 10136</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2157; 8692</t>
+          <t>1642; 8458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>613; 4782</t>
+          <t>877; 6332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1877; 7536</t>
+          <t>638; 5511</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2687; 9777</t>
+          <t>1463; 8427</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1597; 8186</t>
+          <t>2089; 8479</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>908; 6874</t>
+          <t>666; 4896</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3316; 11013</t>
+          <t>3148; 11170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5821; 15389</t>
+          <t>5902; 15280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5266; 14230</t>
+          <t>5116; 14107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2390; 9907</t>
+          <t>2344; 9061</t>
         </is>
       </c>
     </row>
